--- a/AdditionalData/Tables/Compare methods Spiral_IER.xlsx
+++ b/AdditionalData/Tables/Compare methods Spiral_IER.xlsx
@@ -46,22 +46,22 @@
     <t xml:space="preserve">distance blocks Horiz (Km)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sum force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Vert, force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Horiz, force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vert, force blocks row (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horiz, force blocks row (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total force blocks row (GJ)</t>
+    <t xml:space="preserve">Sum force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum Vert, force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum Horiz, force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vert, force blocks row (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horiz, force blocks row (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total force blocks row (MJ)</t>
   </si>
   <si>
     <t xml:space="preserve">% Decrement blocks</t>
@@ -91,6 +91,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -150,8 +151,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -281,135 +286,135 @@
   <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>1985060</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>1025.8</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>1046596.264</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>804122.247</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>242474.071</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>2333681042.84</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>1457688821.871</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>873476798.34</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>13718238.381</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>3764694.11</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>17482864.65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>1985985</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>981.03</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>1024865.54</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>782520.861</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>242344.675</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>2330014190.98</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>1444324141.111</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>886414652.78</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>13409100.541</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>3762924.91</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>17171937.43</v>
       </c>
     </row>
